--- a/Config/Excels/__beans__.xlsx
+++ b/Config/Excels/__beans__.xlsx
@@ -4,30 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowHeight="18450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49">
   <si>
     <t>##var</t>
   </si>
@@ -179,12 +166,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -196,39 +183,69 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -240,19 +257,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -266,80 +290,43 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,43 +335,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -396,19 +455,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,7 +485,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -432,25 +503,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,104 +531,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -581,48 +556,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,17 +580,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,22 +624,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -696,255 +658,222 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="23" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1215,24 +1144,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="22.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="20.6333333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="12.25" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="33.5583333333333" customWidth="1"/>
-    <col min="8" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="16.775" customWidth="1"/>
-    <col min="11" max="11" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.3333333333333" customWidth="1"/>
-    <col min="13" max="13" width="19.4416666666667" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="21.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="7.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="1"/>
+    <col min="15" max="15" width="7" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1259,18 +1193,18 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3"/>
@@ -1281,30 +1215,30 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1321,22 +1255,23 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="O3" s="3"/>
+      <c r="P3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1437,14 +1372,14 @@
       <c r="P7" s="4"/>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
         <v>33</v>
       </c>
@@ -1460,14 +1395,14 @@
       <c r="P8" s="4"/>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
         <v>35</v>
       </c>
@@ -1483,14 +1418,14 @@
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
         <v>37</v>
       </c>
@@ -1506,14 +1441,14 @@
       <c r="P10" s="4"/>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
         <v>39</v>
       </c>
@@ -1529,14 +1464,14 @@
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
         <v>41</v>
       </c>
@@ -1551,182 +1486,69 @@
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="2:14">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-    </row>
-    <row r="14" spans="2:14">
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
+    <row r="13" s="1" customFormat="1"/>
+    <row r="14" spans="2:16">
+      <c r="B14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
     </row>
     <row r="15" spans="2:16">
-      <c r="B15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
     </row>
-    <row r="16" spans="2:16">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-    </row>
-    <row r="17" spans="2:14">
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="2:14">
-      <c r="B18" s="5"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="5"/>
-    </row>
-    <row r="19" ht="27" customHeight="1" spans="2:14">
-      <c r="B19" s="5"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="5"/>
-    </row>
-    <row r="20" spans="2:14">
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="10"/>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="2:14">
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="10"/>
-    </row>
-    <row r="22" spans="2:14">
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="10"/>
-    </row>
-    <row r="24" ht="25" customHeight="1"/>
+    <row r="16" s="1" customFormat="1"/>
+    <row r="17" s="1" customFormat="1"/>
+    <row r="18" s="1" customFormat="1"/>
+    <row r="19" s="1" customFormat="1"/>
+    <row r="20" s="1" customFormat="1"/>
+    <row r="21" s="1" customFormat="1"/>
+    <row r="23" ht="25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>

--- a/Config/Excels/__beans__.xlsx
+++ b/Config/Excels/__beans__.xlsx
@@ -168,10 +168,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -189,6 +189,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
@@ -196,6 +234,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -204,37 +296,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -249,78 +318,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -353,19 +353,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,13 +509,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,139 +521,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,8 +559,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -580,11 +580,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -592,19 +598,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,21 +620,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -653,6 +633,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -661,10 +661,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -673,133 +673,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
